--- a/input/旧版门店清单_2024.xlsx
+++ b/input/旧版门店清单_2024.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,17 +498,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>45640</v>
-      </c>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,12 +526,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>无锡</t>
+          <t>宁波</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -551,22 +549,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>济南</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>45486</v>
-      </c>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -581,12 +577,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>青岛</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -614,12 +610,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南宁</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -637,17 +633,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -665,17 +661,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南宁</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -698,12 +694,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>济南</t>
+          <t>无锡</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -726,7 +722,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>无锡</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -749,17 +745,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -777,22 +773,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>石家庄</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>45397</v>
-      </c>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -807,17 +801,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>济南</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -840,7 +834,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -868,12 +862,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>合肥</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -896,7 +890,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>无锡</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -924,12 +918,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>无锡</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -947,17 +941,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>常州</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>营业</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -980,12 +974,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>合肥</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1003,22 +997,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南宁</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>45458</v>
-      </c>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1043,7 +1035,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1061,17 +1053,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>济南</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1089,12 +1081,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>济南</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1122,17 +1114,15 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>45530</v>
-      </c>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1152,7 +1142,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>厦门</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1175,12 +1165,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>厦门</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1208,7 +1198,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1231,12 +1221,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1259,17 +1249,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>厦门</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1292,12 +1282,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>常州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1315,12 +1305,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1348,7 +1338,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>青岛</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1371,22 +1361,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>45395</v>
-      </c>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1401,12 +1389,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>济南</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1429,22 +1417,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>南宁</t>
+          <t>济南</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>45304</v>
-      </c>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1464,17 +1450,15 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>常州</t>
+          <t>石家庄</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="n">
-        <v>45396</v>
-      </c>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1489,17 +1473,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>济南</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>营业</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1517,12 +1501,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>常州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1550,17 +1534,15 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>常州</t>
+          <t>青岛</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F40" s="1" t="n">
-        <v>45589</v>
-      </c>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1575,22 +1557,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>南宁</t>
+          <t>石家庄</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="n">
-        <v>45639</v>
-      </c>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1610,7 +1590,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>宁波</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1638,17 +1618,15 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>常州</t>
+          <t>青岛</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>关闭</t>
-        </is>
-      </c>
-      <c r="F43" s="1" t="n">
-        <v>45304</v>
-      </c>
+          <t>营业</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1658,25 +1636,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>门店43</t>
+          <t>门店043</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>南宁</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>45346</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1686,7 +1666,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>门店44</t>
+          <t>门店044</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1696,7 +1676,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1705,7 +1685,7 @@
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>45623</v>
+        <v>45381</v>
       </c>
     </row>
     <row r="46">
@@ -1716,7 +1696,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>门店45</t>
+          <t>门店045</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1726,7 +1706,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1735,7 +1715,7 @@
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>45553</v>
+        <v>45412</v>
       </c>
     </row>
     <row r="47">
@@ -1746,7 +1726,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>门店46</t>
+          <t>门店046</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1756,7 +1736,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>石家庄</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1765,7 +1745,7 @@
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>45433</v>
+        <v>45500</v>
       </c>
     </row>
     <row r="48">
@@ -1776,7 +1756,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>门店47</t>
+          <t>门店047</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1786,7 +1766,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>苏州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1795,7 +1775,7 @@
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>45299</v>
+        <v>45444</v>
       </c>
     </row>
     <row r="49">
@@ -1806,7 +1786,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>门店48</t>
+          <t>门店048</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1816,15 +1796,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南宁</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>调整</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>45375</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1834,7 +1816,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>门店49</t>
+          <t>门店049</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1844,15 +1826,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>无锡</t>
+          <t>石家庄</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>营业</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>45361</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1862,7 +1846,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>门店50</t>
+          <t>门店050</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1872,15 +1856,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>营业</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>关闭</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>45601</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
